--- a/data/themes/series/series.xlsx
+++ b/data/themes/series/series.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="series" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="series" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C201"/>
+  <dimension ref="A1:D201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,11 @@
           <t>country</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>only_list</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -602,6 +607,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -687,6 +695,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -806,6 +817,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -840,6 +854,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -857,6 +874,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -891,6 +911,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -908,6 +931,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -925,6 +951,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -993,6 +1022,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1010,6 +1042,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1044,6 +1079,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1146,6 +1184,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1214,6 +1255,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1282,6 +1326,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1316,6 +1363,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1350,6 +1400,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1367,6 +1420,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1384,6 +1440,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1401,6 +1460,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1418,6 +1480,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1435,6 +1500,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1452,6 +1520,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1469,6 +1540,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1503,6 +1577,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1520,6 +1597,9 @@
           <t>США; Великобритания</t>
         </is>
       </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1605,6 +1685,9 @@
           <t>США; Колумбия</t>
         </is>
       </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1656,6 +1739,9 @@
           <t>Великобритания</t>
         </is>
       </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1707,6 +1793,9 @@
           <t>Великобритания</t>
         </is>
       </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1741,6 +1830,9 @@
           <t>Великобритания</t>
         </is>
       </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1758,6 +1850,9 @@
           <t>Великобритания</t>
         </is>
       </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1775,6 +1870,9 @@
           <t>Великобритания</t>
         </is>
       </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1792,6 +1890,9 @@
           <t>Великобритания</t>
         </is>
       </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1826,6 +1927,9 @@
           <t>Великобритания; США</t>
         </is>
       </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1843,6 +1947,9 @@
           <t>Великобритания</t>
         </is>
       </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1860,6 +1967,9 @@
           <t>Великобритания</t>
         </is>
       </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1877,6 +1987,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1911,6 +2024,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1979,6 +2095,9 @@
           <t>СССР</t>
         </is>
       </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1996,6 +2115,9 @@
           <t>СССР</t>
         </is>
       </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2013,6 +2135,9 @@
           <t>СССР</t>
         </is>
       </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2030,6 +2155,9 @@
           <t>СССР</t>
         </is>
       </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2047,6 +2175,9 @@
           <t>СССР</t>
         </is>
       </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2064,6 +2195,9 @@
           <t>СССР</t>
         </is>
       </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2081,6 +2215,9 @@
           <t>СССР</t>
         </is>
       </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2098,6 +2235,9 @@
           <t>СССР</t>
         </is>
       </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2115,6 +2255,9 @@
           <t>СССР</t>
         </is>
       </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2149,6 +2292,9 @@
           <t>СССР</t>
         </is>
       </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2302,6 +2448,9 @@
           <t>Россия; Украина</t>
         </is>
       </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2319,6 +2468,9 @@
           <t>Россия</t>
         </is>
       </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2421,6 +2573,9 @@
           <t>Россия</t>
         </is>
       </c>
+      <c r="D118" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2438,6 +2593,9 @@
           <t>Россия</t>
         </is>
       </c>
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2455,6 +2613,9 @@
           <t>Россия</t>
         </is>
       </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2489,6 +2650,9 @@
           <t>Россия</t>
         </is>
       </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2523,6 +2687,9 @@
           <t>Россия</t>
         </is>
       </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2540,6 +2707,9 @@
           <t>Россия</t>
         </is>
       </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2557,6 +2727,9 @@
           <t>Россия</t>
         </is>
       </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2574,6 +2747,9 @@
           <t>Россия</t>
         </is>
       </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2591,6 +2767,9 @@
           <t>Россия</t>
         </is>
       </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2608,6 +2787,9 @@
           <t>Россия</t>
         </is>
       </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2625,6 +2807,9 @@
           <t>Россия</t>
         </is>
       </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2642,6 +2827,9 @@
           <t>Россия</t>
         </is>
       </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2659,6 +2847,9 @@
           <t>Россия</t>
         </is>
       </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2676,6 +2867,9 @@
           <t>Россия</t>
         </is>
       </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2693,6 +2887,9 @@
           <t>Россия</t>
         </is>
       </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2710,6 +2907,9 @@
           <t>Россия</t>
         </is>
       </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2727,6 +2927,9 @@
           <t>Польша</t>
         </is>
       </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2744,6 +2947,9 @@
           <t>Польша</t>
         </is>
       </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2778,6 +2984,9 @@
           <t>Испания</t>
         </is>
       </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2829,6 +3038,9 @@
           <t>Германия</t>
         </is>
       </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2880,6 +3092,9 @@
           <t>Дания</t>
         </is>
       </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2931,6 +3146,9 @@
           <t>Норвегия; США</t>
         </is>
       </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2982,6 +3200,9 @@
           <t>Франция</t>
         </is>
       </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3050,6 +3271,9 @@
           <t>Израиль</t>
         </is>
       </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3067,6 +3291,9 @@
           <t>Израиль</t>
         </is>
       </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3118,6 +3345,9 @@
           <t>Мексика</t>
         </is>
       </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3135,6 +3365,9 @@
           <t>Мексика</t>
         </is>
       </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3152,6 +3385,9 @@
           <t>Канада</t>
         </is>
       </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3169,6 +3405,9 @@
           <t>Австралия</t>
         </is>
       </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3186,6 +3425,9 @@
           <t>Австралия</t>
         </is>
       </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3203,6 +3445,9 @@
           <t>Индия</t>
         </is>
       </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3237,6 +3482,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3271,6 +3519,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
+      <c r="D168" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3288,6 +3539,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
+      <c r="D169" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3305,6 +3559,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
+      <c r="D170" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3322,6 +3579,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
+      <c r="D171" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3339,6 +3599,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
+      <c r="D172" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3356,6 +3619,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3390,6 +3656,9 @@
           <t>Япония</t>
         </is>
       </c>
+      <c r="D175" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3458,6 +3727,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D179" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3475,6 +3747,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D180" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -3526,6 +3801,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D183" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3543,6 +3821,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D184" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -3577,6 +3858,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D186" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3594,6 +3878,9 @@
           <t>США; Канада</t>
         </is>
       </c>
+      <c r="D187" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -3611,6 +3898,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D188" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -3645,6 +3935,9 @@
           <t>США; Великобритания</t>
         </is>
       </c>
+      <c r="D190" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -3662,6 +3955,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D191" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -3679,6 +3975,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D192" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -3696,6 +3995,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D193" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -3713,6 +4015,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D194" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -3730,6 +4035,9 @@
           <t>Великобритания; США</t>
         </is>
       </c>
+      <c r="D195" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -3747,6 +4055,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D196" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -3764,6 +4075,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D197" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -3798,6 +4112,9 @@
           <t>США</t>
         </is>
       </c>
+      <c r="D199" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -3815,6 +4132,9 @@
           <t>Аргентина</t>
         </is>
       </c>
+      <c r="D200" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -3831,6 +4151,9 @@
         <is>
           <t>США</t>
         </is>
+      </c>
+      <c r="D201" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
